--- a/data/trans_orig/IP07KS_C05_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C05_2023-Clase-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tener suficiente tiempo para sí mismo/a en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de tener suficiente tiempo para sí mismo/a, percibida por el/la menor en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16432</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10870</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>22322</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>41,21%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>27,26%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>55,97%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>11811</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7465</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16697</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>38,74%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>24,49%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>54,77%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16537</t>
+          <t>11995</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11174</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21732</t>
+          <t>16634</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>28347</t>
+          <t>28427</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21193</t>
+          <t>21432</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34594</t>
+          <t>35905</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,93%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17044</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11601</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22618</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>42,74%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>29,09%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>56,72%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>15027</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10452</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>19671</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>49,29%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>34,28%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>64,52%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16592</t>
+          <t>16027</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11610</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22051</t>
+          <t>20544</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>31618</t>
+          <t>33071</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25171</t>
+          <t>25581</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39067</t>
+          <t>40420</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,21%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>532</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>6910</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>753</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5864</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>4441</t>
+          <t>4769</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1666</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9340</t>
+          <t>10088</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3061</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>986</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7127</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,68%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17,87%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>799</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>881</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3226</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3669</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,58%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2898</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>859</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7203</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,41%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>9043</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>928</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3538</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>771</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>3921</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>6211</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>39879</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>30487</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>69611</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12364</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7878</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18452</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>37,25%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>23,73%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>55,59%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>11086</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7071</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15755</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>38,01%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>24,24%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>54,01%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>12380</t>
+          <t>11580</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7539</t>
+          <t>7177</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17912</t>
+          <t>16437</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>23945</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16670</t>
+          <t>17638</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29783</t>
+          <t>31346</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>49,0%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13714</t>
+          <t>14053</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9197</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18098</t>
+          <t>19473</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13390</t>
+          <t>14450</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>10304</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18356</t>
+          <t>19571</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>27104</t>
+          <t>28503</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21208</t>
+          <t>21166</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34412</t>
+          <t>35694</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,8%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>3420</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>900</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6928</t>
+          <t>7818</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>873</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8748</t>
+          <t>7369</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11569</t>
+          <t>11814</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,47%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1526</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7822</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>23,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1438</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1528</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4804</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5434</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4,97%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>16,47%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1516</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6089</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,22 +1816,22 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>633</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9200</t>
+          <t>8769</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -1854,107 +1854,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1831</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5712</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>17,21%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1750</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1831</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5264</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>5,4%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6171</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>16,23%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1750</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>5437</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>63966</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13972</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8958</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>18664</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>51,8%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>33,21%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>69,19%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>4236</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1739</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7593</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>29,12%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11,95%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>52,19%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14172</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9051</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19315</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>18408</t>
+          <t>18317</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12311</t>
+          <t>12977</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24523</t>
+          <t>24535</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,68%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>8936</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4842</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>14205</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>33,13%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>17,95%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>52,66%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>6255</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>9305</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>42,99%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>20,87%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>63,96%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8642</t>
+          <t>6985</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>3463</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13578</t>
+          <t>10292</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>14897</t>
+          <t>15921</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9553</t>
+          <t>10699</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20421</t>
+          <t>22144</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>52,05%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1176</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>4926</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4,36%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>18,26%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>3295</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1194</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6262</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>22,65%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>8,21%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>43,04%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4865</t>
+          <t>6953</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1734</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8668</t>
+          <t>8758</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>601</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3612</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>828</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>4608</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -2536,107 +2536,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2288</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>7631</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>8,48%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>28,29%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>2919</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>2288</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>8752</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>10,54%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>7435</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>31,61%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>2919</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>9638</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>6,91%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>26973</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>14549</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>34850</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>24437</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>44651</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>50,21%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>35,2%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>64,33%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>16755</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>5044</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>31458</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>25,24%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>7,6%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>47,38%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>35435</t>
+          <t>17349</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24292</t>
+          <t>11461</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46157</t>
+          <t>23284</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>52190</t>
+          <t>52198</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27815</t>
+          <t>39569</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>70793</t>
+          <t>63911</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>56,94%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>24614</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>15152</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>34958</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>35,46%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>21,83%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>50,36%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>41945</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>22458</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>57852</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>63,18%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>33,83%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>87,14%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>25436</t>
+          <t>17484</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>16237</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>37913</t>
+          <t>23540</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>67380</t>
+          <t>42099</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>45786</t>
+          <t>31547</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>99982</t>
+          <t>54236</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>48,32%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>3508</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1165</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>9373</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>4951</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>10964</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>7,46%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>16,52%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9151</t>
+          <t>9899</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>8315</t>
+          <t>8658</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15262</t>
+          <t>15839</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>567</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6306</t>
+          <t>6240</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2271</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>579</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>5586</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1581</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9732</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>4413</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1525</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>9713</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>6,36%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>13,99%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>2833</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>4,27%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>4451</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>1602</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>10306</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>6,29%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11626</t>
+          <t>10948</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>69414</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>69414</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>69414</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>66388</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>66388</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>66388</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>42826</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>42826</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>70787</t>
+          <t>42826</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>137175</t>
+          <t>112240</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>137175</t>
+          <t>112240</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>137175</t>
+          <t>112240</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>25547</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>16732</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>39951</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>43,2%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>28,29%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>67,55%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>10844</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>6326</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>15680</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>30,37%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>17,71%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>43,91%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>28168</t>
+          <t>11222</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18358</t>
+          <t>6723</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>44706</t>
+          <t>16929</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>39011</t>
+          <t>36770</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27791</t>
+          <t>26752</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>58225</t>
+          <t>53664</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>54,69%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>22119</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>13129</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>30736</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>37,4%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>51,97%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>19493</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>14973</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>24233</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>54,59%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>41,93%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>67,86%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>21212</t>
+          <t>21639</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9924</t>
+          <t>15465</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29954</t>
+          <t>26684</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>40705</t>
+          <t>43759</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27289</t>
+          <t>31276</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>51637</t>
+          <t>53487</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>54,51%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>8848</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>3395</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>15459</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>14,96%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>5,74%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>26,14%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>5373</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>2464</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>9638</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>15,05%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>6,9%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>26,99%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>8652</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16265</t>
+          <t>11673</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>14025</t>
+          <t>14963</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>8309</t>
+          <t>9354</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>21558</t>
+          <t>23514</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -3787,107 +3787,107 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>863</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>4013</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>6,79%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>850</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>863</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>5164</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>4170</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>8,5%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>850</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>4720</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -3900,107 +3900,107 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>1764</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>7045</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>11,91%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>1899</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>1764</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>6766</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>6030</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>11,13%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>1899</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>7028</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>59142</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>59142</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>59142</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>60781</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>60781</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>60781</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>96491</t>
+          <t>98118</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>96491</t>
+          <t>98118</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>96491</t>
+          <t>98118</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4130,72 +4130,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>11274</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>6840</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>17171</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>30,87%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>18,73%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>47,02%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>9138</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>5354</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>13949</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>30,28%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>17,74%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>46,22%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>11411</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>5833</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>17072</t>
+          <t>15416</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>20549</t>
+          <t>21182</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>14347</t>
+          <t>14957</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>27451</t>
+          <t>28211</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>40,5%</t>
         </is>
       </c>
     </row>
@@ -4243,72 +4243,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>21255</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>15553</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>26327</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>58,2%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>42,59%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>72,09%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>12399</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>8125</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>16380</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>41,09%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>26,92%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>54,28%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>20985</t>
+          <t>13527</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>15158</t>
+          <t>8763</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>26012</t>
+          <t>18764</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>33384</t>
+          <t>34782</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>26806</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>41105</t>
+          <t>42120</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>60,47%</t>
         </is>
       </c>
     </row>
@@ -4356,72 +4356,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>3038</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>7209</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>8,32%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>19,74%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>7534</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>3726</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>12767</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>24,97%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>12,35%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>42,31%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2762</t>
+          <t>8764</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>4376</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7182</t>
+          <t>14814</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>10296</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5720</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>16623</t>
+          <t>19622</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>28,17%</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>953</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>4864</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>931</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>3994</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
@@ -4554,12 +4554,12 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6265</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -4695,57 +4695,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>36521</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>36521</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>36521</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>30177</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>30177</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>30177</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>36068</t>
+          <t>33129</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4812,72 +4812,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>114440</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>97591</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>137315</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>43,16%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>36,81%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>51,79%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>63870</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>40514</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>79262</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>30,93%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>19,62%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>38,39%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>118102</t>
+          <t>66399</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>99183</t>
+          <t>54632</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>138185</t>
+          <t>77010</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>181972</t>
+          <t>180839</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>148770</t>
+          <t>160435</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>210734</t>
+          <t>205960</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,93%</t>
         </is>
       </c>
     </row>
@@ -4925,72 +4925,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>108023</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>88802</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>125399</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>40,74%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>33,49%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>47,3%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>108833</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>88931</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>142319</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>52,71%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>68,93%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>106256</t>
+          <t>90112</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>89021</t>
+          <t>78855</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>123383</t>
+          <t>103253</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>215089</t>
+          <t>198135</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>187480</t>
+          <t>178231</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>219198</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>47,82%</t>
         </is>
       </c>
     </row>
@@ -5038,72 +5038,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>22403</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>14521</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>32987</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>5,48%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>12,44%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>26242</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>16858</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>36352</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>12,71%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>8,16%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>17,61%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>21775</t>
+          <t>29005</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>14627</t>
+          <t>20901</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>31980</t>
+          <t>39188</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>48017</t>
+          <t>51409</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>35651</t>
+          <t>40033</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>63642</t>
+          <t>66146</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -5151,72 +5151,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>9034</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>4743</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>15963</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>6299</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>2610</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>12403</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>6,01%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>8916</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>15409</t>
+          <t>12073</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>15215</t>
+          <t>15473</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>9268</t>
+          <t>9560</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>24058</t>
+          <t>24311</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -5264,72 +5264,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>11225</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>6026</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>18813</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>1236</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>1344</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>4430</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>4834</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>11834</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>6178</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>21105</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>13070</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>7227</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>21499</t>
+          <t>21239</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>265125</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>265125</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>265125</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>206479</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>206479</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>206479</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>266883</t>
+          <t>193299</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>266883</t>
+          <t>193299</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>266883</t>
+          <t>193299</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>473362</t>
+          <t>458424</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>473362</t>
+          <t>458424</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>473362</t>
+          <t>458424</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
